--- a/docs/Mapping_casi_uso/matrimoni/Matr_999_3.xlsx
+++ b/docs/Mapping_casi_uso/matrimoni/Matr_999_3.xlsx
@@ -12,7 +12,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="742" uniqueCount="162">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="770" uniqueCount="166">
   <si>
     <t>Sezione</t>
   </si>
@@ -446,6 +446,12 @@
     <t>flagFirmatario</t>
   </si>
   <si>
+    <t>Età(anni)</t>
+  </si>
+  <si>
+    <t>anni</t>
+  </si>
+  <si>
     <t>Provincia AIRE</t>
   </si>
   <si>
@@ -468,6 +474,12 @@
   </si>
   <si>
     <t>nomeComuneAIRE</t>
+  </si>
+  <si>
+    <t>Residenza al momento dell'evento originario</t>
+  </si>
+  <si>
+    <t>residenzaOriginaria</t>
   </si>
   <si>
     <t>Sposa</t>
@@ -556,7 +568,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <dimension ref="A1:H106"/>
+  <dimension ref="A1:H110"/>
   <sheetFormatPr defaultRowHeight="15.0"/>
   <cols>
     <col min="1" max="1" width="32.98046875" customWidth="true" bestFit="true"/>
@@ -1588,7 +1600,7 @@
         <v>100</v>
       </c>
       <c r="C45" s="2" t="s">
-        <v>17</v>
+        <v>9</v>
       </c>
       <c r="D45" s="2" t="s">
         <v>88</v>
@@ -1597,7 +1609,7 @@
         <v>101</v>
       </c>
       <c r="F45" s="2" t="s">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="G45" s="2" t="s">
         <v>38</v>
@@ -1611,7 +1623,7 @@
         <v>102</v>
       </c>
       <c r="C46" s="2" t="s">
-        <v>17</v>
+        <v>9</v>
       </c>
       <c r="D46" s="2" t="s">
         <v>88</v>
@@ -1634,7 +1646,7 @@
         <v>104</v>
       </c>
       <c r="C47" s="2" t="s">
-        <v>17</v>
+        <v>9</v>
       </c>
       <c r="D47" s="2" t="s">
         <v>88</v>
@@ -1643,7 +1655,7 @@
         <v>105</v>
       </c>
       <c r="F47" s="2" t="s">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="G47" s="2" t="s">
         <v>38</v>
@@ -1772,7 +1784,7 @@
         <v>116</v>
       </c>
       <c r="C53" s="2" t="s">
-        <v>17</v>
+        <v>9</v>
       </c>
       <c r="D53" s="2" t="s">
         <v>88</v>
@@ -1795,7 +1807,7 @@
         <v>118</v>
       </c>
       <c r="C54" s="2" t="s">
-        <v>17</v>
+        <v>9</v>
       </c>
       <c r="D54" s="2" t="s">
         <v>88</v>
@@ -1804,7 +1816,7 @@
         <v>119</v>
       </c>
       <c r="F54" s="2" t="s">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="G54" s="2" t="s">
         <v>38</v>
@@ -2180,22 +2192,22 @@
     </row>
     <row r="71">
       <c r="A71" s="2" t="s">
+        <v>86</v>
+      </c>
+      <c r="B71" s="2" t="s">
         <v>152</v>
       </c>
-      <c r="B71" s="2" t="s">
-        <v>87</v>
-      </c>
       <c r="C71" s="2" t="s">
         <v>9</v>
       </c>
       <c r="D71" s="2" t="s">
+        <v>88</v>
+      </c>
+      <c r="E71" s="2" t="s">
         <v>153</v>
       </c>
-      <c r="E71" s="2" t="s">
-        <v>89</v>
-      </c>
       <c r="F71" s="2" t="s">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="G71" s="2" t="s">
         <v>38</v>
@@ -2203,19 +2215,19 @@
     </row>
     <row r="72">
       <c r="A72" s="2" t="s">
-        <v>152</v>
+        <v>86</v>
       </c>
       <c r="B72" s="2" t="s">
-        <v>90</v>
+        <v>154</v>
       </c>
       <c r="C72" s="2" t="s">
-        <v>17</v>
+        <v>9</v>
       </c>
       <c r="D72" s="2" t="s">
-        <v>153</v>
+        <v>88</v>
       </c>
       <c r="E72" s="2" t="s">
-        <v>91</v>
+        <v>155</v>
       </c>
       <c r="F72" s="2" t="s">
         <v>10</v>
@@ -2226,22 +2238,22 @@
     </row>
     <row r="73">
       <c r="A73" s="2" t="s">
-        <v>152</v>
+        <v>156</v>
       </c>
       <c r="B73" s="2" t="s">
-        <v>92</v>
+        <v>87</v>
       </c>
       <c r="C73" s="2" t="s">
         <v>9</v>
       </c>
       <c r="D73" s="2" t="s">
-        <v>153</v>
+        <v>157</v>
       </c>
       <c r="E73" s="2" t="s">
-        <v>93</v>
+        <v>89</v>
       </c>
       <c r="F73" s="2" t="s">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="G73" s="2" t="s">
         <v>38</v>
@@ -2249,19 +2261,19 @@
     </row>
     <row r="74">
       <c r="A74" s="2" t="s">
-        <v>152</v>
+        <v>156</v>
       </c>
       <c r="B74" s="2" t="s">
-        <v>94</v>
+        <v>90</v>
       </c>
       <c r="C74" s="2" t="s">
         <v>17</v>
       </c>
       <c r="D74" s="2" t="s">
-        <v>153</v>
+        <v>157</v>
       </c>
       <c r="E74" s="2" t="s">
-        <v>95</v>
+        <v>91</v>
       </c>
       <c r="F74" s="2" t="s">
         <v>10</v>
@@ -2272,19 +2284,19 @@
     </row>
     <row r="75">
       <c r="A75" s="2" t="s">
-        <v>152</v>
+        <v>156</v>
       </c>
       <c r="B75" s="2" t="s">
-        <v>96</v>
+        <v>92</v>
       </c>
       <c r="C75" s="2" t="s">
         <v>9</v>
       </c>
       <c r="D75" s="2" t="s">
-        <v>153</v>
+        <v>157</v>
       </c>
       <c r="E75" s="2" t="s">
-        <v>97</v>
+        <v>93</v>
       </c>
       <c r="F75" s="2" t="s">
         <v>10</v>
@@ -2295,19 +2307,19 @@
     </row>
     <row r="76">
       <c r="A76" s="2" t="s">
-        <v>152</v>
+        <v>156</v>
       </c>
       <c r="B76" s="2" t="s">
-        <v>98</v>
+        <v>94</v>
       </c>
       <c r="C76" s="2" t="s">
-        <v>9</v>
+        <v>17</v>
       </c>
       <c r="D76" s="2" t="s">
-        <v>153</v>
+        <v>157</v>
       </c>
       <c r="E76" s="2" t="s">
-        <v>99</v>
+        <v>95</v>
       </c>
       <c r="F76" s="2" t="s">
         <v>10</v>
@@ -2318,19 +2330,19 @@
     </row>
     <row r="77">
       <c r="A77" s="2" t="s">
-        <v>152</v>
+        <v>156</v>
       </c>
       <c r="B77" s="2" t="s">
-        <v>100</v>
+        <v>96</v>
       </c>
       <c r="C77" s="2" t="s">
-        <v>17</v>
+        <v>9</v>
       </c>
       <c r="D77" s="2" t="s">
-        <v>153</v>
+        <v>157</v>
       </c>
       <c r="E77" s="2" t="s">
-        <v>101</v>
+        <v>97</v>
       </c>
       <c r="F77" s="2" t="s">
         <v>10</v>
@@ -2341,19 +2353,19 @@
     </row>
     <row r="78">
       <c r="A78" s="2" t="s">
-        <v>152</v>
+        <v>156</v>
       </c>
       <c r="B78" s="2" t="s">
-        <v>102</v>
+        <v>98</v>
       </c>
       <c r="C78" s="2" t="s">
-        <v>17</v>
+        <v>9</v>
       </c>
       <c r="D78" s="2" t="s">
-        <v>153</v>
+        <v>157</v>
       </c>
       <c r="E78" s="2" t="s">
-        <v>103</v>
+        <v>99</v>
       </c>
       <c r="F78" s="2" t="s">
         <v>10</v>
@@ -2364,22 +2376,22 @@
     </row>
     <row r="79">
       <c r="A79" s="2" t="s">
-        <v>152</v>
+        <v>156</v>
       </c>
       <c r="B79" s="2" t="s">
-        <v>104</v>
+        <v>100</v>
       </c>
       <c r="C79" s="2" t="s">
-        <v>17</v>
+        <v>9</v>
       </c>
       <c r="D79" s="2" t="s">
-        <v>153</v>
+        <v>157</v>
       </c>
       <c r="E79" s="2" t="s">
-        <v>105</v>
+        <v>101</v>
       </c>
       <c r="F79" s="2" t="s">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="G79" s="2" t="s">
         <v>38</v>
@@ -2387,19 +2399,19 @@
     </row>
     <row r="80">
       <c r="A80" s="2" t="s">
-        <v>152</v>
+        <v>156</v>
       </c>
       <c r="B80" s="2" t="s">
-        <v>106</v>
+        <v>102</v>
       </c>
       <c r="C80" s="2" t="s">
         <v>9</v>
       </c>
       <c r="D80" s="2" t="s">
-        <v>153</v>
+        <v>157</v>
       </c>
       <c r="E80" s="2" t="s">
-        <v>107</v>
+        <v>103</v>
       </c>
       <c r="F80" s="2" t="s">
         <v>10</v>
@@ -2410,19 +2422,19 @@
     </row>
     <row r="81">
       <c r="A81" s="2" t="s">
-        <v>152</v>
+        <v>156</v>
       </c>
       <c r="B81" s="2" t="s">
-        <v>108</v>
+        <v>104</v>
       </c>
       <c r="C81" s="2" t="s">
         <v>9</v>
       </c>
       <c r="D81" s="2" t="s">
-        <v>153</v>
+        <v>157</v>
       </c>
       <c r="E81" s="2" t="s">
-        <v>109</v>
+        <v>105</v>
       </c>
       <c r="F81" s="2" t="s">
         <v>12</v>
@@ -2433,19 +2445,19 @@
     </row>
     <row r="82">
       <c r="A82" s="2" t="s">
-        <v>152</v>
+        <v>156</v>
       </c>
       <c r="B82" s="2" t="s">
-        <v>110</v>
+        <v>106</v>
       </c>
       <c r="C82" s="2" t="s">
         <v>9</v>
       </c>
       <c r="D82" s="2" t="s">
-        <v>153</v>
+        <v>157</v>
       </c>
       <c r="E82" s="2" t="s">
-        <v>111</v>
+        <v>107</v>
       </c>
       <c r="F82" s="2" t="s">
         <v>10</v>
@@ -2456,19 +2468,19 @@
     </row>
     <row r="83">
       <c r="A83" s="2" t="s">
-        <v>152</v>
+        <v>156</v>
       </c>
       <c r="B83" s="2" t="s">
-        <v>112</v>
+        <v>108</v>
       </c>
       <c r="C83" s="2" t="s">
         <v>9</v>
       </c>
       <c r="D83" s="2" t="s">
-        <v>153</v>
+        <v>157</v>
       </c>
       <c r="E83" s="2" t="s">
-        <v>113</v>
+        <v>109</v>
       </c>
       <c r="F83" s="2" t="s">
         <v>12</v>
@@ -2479,22 +2491,22 @@
     </row>
     <row r="84">
       <c r="A84" s="2" t="s">
-        <v>152</v>
+        <v>156</v>
       </c>
       <c r="B84" s="2" t="s">
-        <v>114</v>
+        <v>110</v>
       </c>
       <c r="C84" s="2" t="s">
         <v>9</v>
       </c>
       <c r="D84" s="2" t="s">
-        <v>153</v>
+        <v>157</v>
       </c>
       <c r="E84" s="2" t="s">
-        <v>115</v>
+        <v>111</v>
       </c>
       <c r="F84" s="2" t="s">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="G84" s="2" t="s">
         <v>38</v>
@@ -2502,22 +2514,22 @@
     </row>
     <row r="85">
       <c r="A85" s="2" t="s">
-        <v>152</v>
+        <v>156</v>
       </c>
       <c r="B85" s="2" t="s">
-        <v>116</v>
+        <v>112</v>
       </c>
       <c r="C85" s="2" t="s">
-        <v>17</v>
+        <v>9</v>
       </c>
       <c r="D85" s="2" t="s">
-        <v>153</v>
+        <v>157</v>
       </c>
       <c r="E85" s="2" t="s">
-        <v>117</v>
+        <v>113</v>
       </c>
       <c r="F85" s="2" t="s">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="G85" s="2" t="s">
         <v>38</v>
@@ -2525,22 +2537,22 @@
     </row>
     <row r="86">
       <c r="A86" s="2" t="s">
-        <v>152</v>
+        <v>156</v>
       </c>
       <c r="B86" s="2" t="s">
-        <v>118</v>
+        <v>114</v>
       </c>
       <c r="C86" s="2" t="s">
-        <v>17</v>
+        <v>9</v>
       </c>
       <c r="D86" s="2" t="s">
-        <v>153</v>
+        <v>157</v>
       </c>
       <c r="E86" s="2" t="s">
-        <v>119</v>
+        <v>115</v>
       </c>
       <c r="F86" s="2" t="s">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="G86" s="2" t="s">
         <v>38</v>
@@ -2548,19 +2560,19 @@
     </row>
     <row r="87">
       <c r="A87" s="2" t="s">
-        <v>152</v>
+        <v>156</v>
       </c>
       <c r="B87" s="2" t="s">
-        <v>120</v>
+        <v>116</v>
       </c>
       <c r="C87" s="2" t="s">
         <v>9</v>
       </c>
       <c r="D87" s="2" t="s">
-        <v>153</v>
+        <v>157</v>
       </c>
       <c r="E87" s="2" t="s">
-        <v>121</v>
+        <v>117</v>
       </c>
       <c r="F87" s="2" t="s">
         <v>10</v>
@@ -2571,22 +2583,22 @@
     </row>
     <row r="88">
       <c r="A88" s="2" t="s">
-        <v>152</v>
+        <v>156</v>
       </c>
       <c r="B88" s="2" t="s">
-        <v>122</v>
+        <v>118</v>
       </c>
       <c r="C88" s="2" t="s">
         <v>9</v>
       </c>
       <c r="D88" s="2" t="s">
-        <v>153</v>
+        <v>157</v>
       </c>
       <c r="E88" s="2" t="s">
-        <v>123</v>
+        <v>119</v>
       </c>
       <c r="F88" s="2" t="s">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="G88" s="2" t="s">
         <v>38</v>
@@ -2594,19 +2606,19 @@
     </row>
     <row r="89">
       <c r="A89" s="2" t="s">
-        <v>152</v>
+        <v>156</v>
       </c>
       <c r="B89" s="2" t="s">
-        <v>124</v>
+        <v>120</v>
       </c>
       <c r="C89" s="2" t="s">
         <v>9</v>
       </c>
       <c r="D89" s="2" t="s">
-        <v>153</v>
+        <v>157</v>
       </c>
       <c r="E89" s="2" t="s">
-        <v>125</v>
+        <v>121</v>
       </c>
       <c r="F89" s="2" t="s">
         <v>10</v>
@@ -2617,22 +2629,22 @@
     </row>
     <row r="90">
       <c r="A90" s="2" t="s">
-        <v>152</v>
+        <v>156</v>
       </c>
       <c r="B90" s="2" t="s">
-        <v>126</v>
+        <v>122</v>
       </c>
       <c r="C90" s="2" t="s">
         <v>9</v>
       </c>
       <c r="D90" s="2" t="s">
-        <v>153</v>
+        <v>157</v>
       </c>
       <c r="E90" s="2" t="s">
-        <v>127</v>
+        <v>123</v>
       </c>
       <c r="F90" s="2" t="s">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="G90" s="2" t="s">
         <v>38</v>
@@ -2640,19 +2652,19 @@
     </row>
     <row r="91">
       <c r="A91" s="2" t="s">
-        <v>152</v>
+        <v>156</v>
       </c>
       <c r="B91" s="2" t="s">
-        <v>128</v>
+        <v>124</v>
       </c>
       <c r="C91" s="2" t="s">
         <v>9</v>
       </c>
       <c r="D91" s="2" t="s">
-        <v>153</v>
+        <v>157</v>
       </c>
       <c r="E91" s="2" t="s">
-        <v>129</v>
+        <v>125</v>
       </c>
       <c r="F91" s="2" t="s">
         <v>10</v>
@@ -2663,19 +2675,19 @@
     </row>
     <row r="92">
       <c r="A92" s="2" t="s">
-        <v>152</v>
+        <v>156</v>
       </c>
       <c r="B92" s="2" t="s">
-        <v>130</v>
+        <v>126</v>
       </c>
       <c r="C92" s="2" t="s">
         <v>9</v>
       </c>
       <c r="D92" s="2" t="s">
-        <v>153</v>
+        <v>157</v>
       </c>
       <c r="E92" s="2" t="s">
-        <v>131</v>
+        <v>127</v>
       </c>
       <c r="F92" s="2" t="s">
         <v>12</v>
@@ -2686,19 +2698,19 @@
     </row>
     <row r="93">
       <c r="A93" s="2" t="s">
-        <v>152</v>
+        <v>156</v>
       </c>
       <c r="B93" s="2" t="s">
-        <v>132</v>
+        <v>128</v>
       </c>
       <c r="C93" s="2" t="s">
         <v>9</v>
       </c>
       <c r="D93" s="2" t="s">
-        <v>153</v>
+        <v>157</v>
       </c>
       <c r="E93" s="2" t="s">
-        <v>133</v>
+        <v>129</v>
       </c>
       <c r="F93" s="2" t="s">
         <v>10</v>
@@ -2709,19 +2721,19 @@
     </row>
     <row r="94">
       <c r="A94" s="2" t="s">
-        <v>152</v>
+        <v>156</v>
       </c>
       <c r="B94" s="2" t="s">
-        <v>134</v>
+        <v>130</v>
       </c>
       <c r="C94" s="2" t="s">
         <v>9</v>
       </c>
       <c r="D94" s="2" t="s">
-        <v>153</v>
+        <v>157</v>
       </c>
       <c r="E94" s="2" t="s">
-        <v>135</v>
+        <v>131</v>
       </c>
       <c r="F94" s="2" t="s">
         <v>12</v>
@@ -2732,22 +2744,22 @@
     </row>
     <row r="95">
       <c r="A95" s="2" t="s">
-        <v>152</v>
+        <v>156</v>
       </c>
       <c r="B95" s="2" t="s">
-        <v>136</v>
+        <v>132</v>
       </c>
       <c r="C95" s="2" t="s">
         <v>9</v>
       </c>
       <c r="D95" s="2" t="s">
-        <v>153</v>
+        <v>157</v>
       </c>
       <c r="E95" s="2" t="s">
-        <v>137</v>
+        <v>133</v>
       </c>
       <c r="F95" s="2" t="s">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="G95" s="2" t="s">
         <v>38</v>
@@ -2755,22 +2767,22 @@
     </row>
     <row r="96">
       <c r="A96" s="2" t="s">
-        <v>152</v>
+        <v>156</v>
       </c>
       <c r="B96" s="2" t="s">
-        <v>138</v>
+        <v>134</v>
       </c>
       <c r="C96" s="2" t="s">
-        <v>17</v>
+        <v>9</v>
       </c>
       <c r="D96" s="2" t="s">
-        <v>153</v>
+        <v>157</v>
       </c>
       <c r="E96" s="2" t="s">
-        <v>139</v>
+        <v>135</v>
       </c>
       <c r="F96" s="2" t="s">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="G96" s="2" t="s">
         <v>38</v>
@@ -2778,22 +2790,22 @@
     </row>
     <row r="97">
       <c r="A97" s="2" t="s">
-        <v>152</v>
+        <v>156</v>
       </c>
       <c r="B97" s="2" t="s">
-        <v>140</v>
+        <v>136</v>
       </c>
       <c r="C97" s="2" t="s">
-        <v>17</v>
+        <v>9</v>
       </c>
       <c r="D97" s="2" t="s">
-        <v>153</v>
+        <v>157</v>
       </c>
       <c r="E97" s="2" t="s">
-        <v>141</v>
+        <v>137</v>
       </c>
       <c r="F97" s="2" t="s">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="G97" s="2" t="s">
         <v>38</v>
@@ -2801,19 +2813,19 @@
     </row>
     <row r="98">
       <c r="A98" s="2" t="s">
-        <v>152</v>
+        <v>156</v>
       </c>
       <c r="B98" s="2" t="s">
-        <v>142</v>
+        <v>138</v>
       </c>
       <c r="C98" s="2" t="s">
-        <v>9</v>
+        <v>17</v>
       </c>
       <c r="D98" s="2" t="s">
-        <v>153</v>
+        <v>157</v>
       </c>
       <c r="E98" s="2" t="s">
-        <v>143</v>
+        <v>139</v>
       </c>
       <c r="F98" s="2" t="s">
         <v>10</v>
@@ -2824,19 +2836,19 @@
     </row>
     <row r="99">
       <c r="A99" s="2" t="s">
-        <v>152</v>
+        <v>156</v>
       </c>
       <c r="B99" s="2" t="s">
-        <v>144</v>
+        <v>140</v>
       </c>
       <c r="C99" s="2" t="s">
-        <v>9</v>
+        <v>17</v>
       </c>
       <c r="D99" s="2" t="s">
-        <v>153</v>
+        <v>157</v>
       </c>
       <c r="E99" s="2" t="s">
-        <v>145</v>
+        <v>141</v>
       </c>
       <c r="F99" s="2" t="s">
         <v>10</v>
@@ -2847,19 +2859,19 @@
     </row>
     <row r="100">
       <c r="A100" s="2" t="s">
-        <v>152</v>
+        <v>156</v>
       </c>
       <c r="B100" s="2" t="s">
-        <v>146</v>
+        <v>142</v>
       </c>
       <c r="C100" s="2" t="s">
         <v>9</v>
       </c>
       <c r="D100" s="2" t="s">
-        <v>153</v>
+        <v>157</v>
       </c>
       <c r="E100" s="2" t="s">
-        <v>147</v>
+        <v>143</v>
       </c>
       <c r="F100" s="2" t="s">
         <v>10</v>
@@ -2870,19 +2882,19 @@
     </row>
     <row r="101">
       <c r="A101" s="2" t="s">
-        <v>152</v>
+        <v>156</v>
       </c>
       <c r="B101" s="2" t="s">
-        <v>148</v>
+        <v>144</v>
       </c>
       <c r="C101" s="2" t="s">
         <v>9</v>
       </c>
       <c r="D101" s="2" t="s">
-        <v>153</v>
+        <v>157</v>
       </c>
       <c r="E101" s="2" t="s">
-        <v>149</v>
+        <v>145</v>
       </c>
       <c r="F101" s="2" t="s">
         <v>10</v>
@@ -2893,19 +2905,19 @@
     </row>
     <row r="102">
       <c r="A102" s="2" t="s">
-        <v>152</v>
+        <v>156</v>
       </c>
       <c r="B102" s="2" t="s">
-        <v>150</v>
+        <v>146</v>
       </c>
       <c r="C102" s="2" t="s">
         <v>9</v>
       </c>
       <c r="D102" s="2" t="s">
-        <v>153</v>
+        <v>157</v>
       </c>
       <c r="E102" s="2" t="s">
-        <v>151</v>
+        <v>147</v>
       </c>
       <c r="F102" s="2" t="s">
         <v>10</v>
@@ -2916,93 +2928,185 @@
     </row>
     <row r="103">
       <c r="A103" s="2" t="s">
-        <v>154</v>
+        <v>156</v>
       </c>
       <c r="B103" s="2" t="s">
-        <v>28</v>
+        <v>148</v>
       </c>
       <c r="C103" s="2" t="s">
-        <v>17</v>
+        <v>9</v>
       </c>
       <c r="D103" s="2" t="s">
-        <v>29</v>
+        <v>157</v>
       </c>
       <c r="E103" s="2" t="s">
-        <v>155</v>
+        <v>149</v>
       </c>
       <c r="F103" s="2" t="s">
         <v>10</v>
       </c>
       <c r="G103" s="2" t="s">
-        <v>20</v>
+        <v>38</v>
       </c>
     </row>
     <row r="104">
       <c r="A104" s="2" t="s">
-        <v>154</v>
+        <v>156</v>
       </c>
       <c r="B104" s="2" t="s">
-        <v>156</v>
+        <v>150</v>
       </c>
       <c r="C104" s="2" t="s">
         <v>9</v>
       </c>
       <c r="D104" s="2" t="s">
-        <v>29</v>
+        <v>157</v>
       </c>
       <c r="E104" s="2" t="s">
-        <v>157</v>
+        <v>151</v>
       </c>
       <c r="F104" s="2" t="s">
         <v>10</v>
       </c>
       <c r="G104" s="2" t="s">
-        <v>20</v>
+        <v>38</v>
       </c>
     </row>
     <row r="105">
       <c r="A105" s="2" t="s">
-        <v>154</v>
+        <v>156</v>
       </c>
       <c r="B105" s="2" t="s">
-        <v>158</v>
+        <v>152</v>
       </c>
       <c r="C105" s="2" t="s">
         <v>9</v>
       </c>
       <c r="D105" s="2" t="s">
-        <v>29</v>
+        <v>157</v>
       </c>
       <c r="E105" s="2" t="s">
-        <v>159</v>
+        <v>153</v>
       </c>
       <c r="F105" s="2" t="s">
         <v>10</v>
       </c>
       <c r="G105" s="2" t="s">
-        <v>20</v>
+        <v>38</v>
       </c>
     </row>
     <row r="106">
       <c r="A106" s="2" t="s">
+        <v>156</v>
+      </c>
+      <c r="B106" s="2" t="s">
         <v>154</v>
       </c>
-      <c r="B106" s="2" t="s">
+      <c r="C106" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="D106" s="2" t="s">
+        <v>157</v>
+      </c>
+      <c r="E106" s="2" t="s">
+        <v>155</v>
+      </c>
+      <c r="F106" s="2" t="s">
+        <v>10</v>
+      </c>
+      <c r="G106" s="2" t="s">
+        <v>38</v>
+      </c>
+    </row>
+    <row r="107">
+      <c r="A107" s="2" t="s">
+        <v>158</v>
+      </c>
+      <c r="B107" s="2" t="s">
+        <v>28</v>
+      </c>
+      <c r="C107" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="D107" s="2" t="s">
+        <v>29</v>
+      </c>
+      <c r="E107" s="2" t="s">
+        <v>159</v>
+      </c>
+      <c r="F107" s="2" t="s">
+        <v>10</v>
+      </c>
+      <c r="G107" s="2" t="s">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="108">
+      <c r="A108" s="2" t="s">
+        <v>158</v>
+      </c>
+      <c r="B108" s="2" t="s">
         <v>160</v>
       </c>
-      <c r="C106" s="2" t="s">
-        <v>9</v>
-      </c>
-      <c r="D106" s="2" t="s">
+      <c r="C108" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="D108" s="2" t="s">
         <v>29</v>
       </c>
-      <c r="E106" s="2" t="s">
+      <c r="E108" s="2" t="s">
         <v>161</v>
       </c>
-      <c r="F106" s="2" t="s">
-        <v>10</v>
-      </c>
-      <c r="G106" s="2" t="s">
+      <c r="F108" s="2" t="s">
+        <v>10</v>
+      </c>
+      <c r="G108" s="2" t="s">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="109">
+      <c r="A109" s="2" t="s">
+        <v>158</v>
+      </c>
+      <c r="B109" s="2" t="s">
+        <v>162</v>
+      </c>
+      <c r="C109" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="D109" s="2" t="s">
+        <v>29</v>
+      </c>
+      <c r="E109" s="2" t="s">
+        <v>163</v>
+      </c>
+      <c r="F109" s="2" t="s">
+        <v>10</v>
+      </c>
+      <c r="G109" s="2" t="s">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="110">
+      <c r="A110" s="2" t="s">
+        <v>158</v>
+      </c>
+      <c r="B110" s="2" t="s">
+        <v>164</v>
+      </c>
+      <c r="C110" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="D110" s="2" t="s">
+        <v>29</v>
+      </c>
+      <c r="E110" s="2" t="s">
+        <v>165</v>
+      </c>
+      <c r="F110" s="2" t="s">
+        <v>10</v>
+      </c>
+      <c r="G110" s="2" t="s">
         <v>20</v>
       </c>
     </row>
